--- a/selenium-tests/selenium-test-report.xlsx
+++ b/selenium-tests/selenium-test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="360">
   <si>
     <t>Test ID</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Loaded page successfully</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:53.054Z</t>
+    <t>2026-07-22T04:27:28.025Z</t>
   </si>
   <si>
     <t>Authentication</t>
@@ -68,7 +68,7 @@
     <t>Tabs found on UI</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:53.217Z</t>
+    <t>2026-07-22T04:27:28.245Z</t>
   </si>
   <si>
     <t>Click email tab and check input fields</t>
@@ -80,7 +80,7 @@
     <t>Email login mode activated</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:53.826Z</t>
+    <t>2026-07-22T04:27:29.170Z</t>
   </si>
   <si>
     <t>Submit login form empty</t>
@@ -92,7 +92,7 @@
     <t>HTML5 validation or custom form checking succeeded</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:54.077Z</t>
+    <t>2026-07-22T04:27:29.558Z</t>
   </si>
   <si>
     <t>Registration Password Boundary Check - Length 3</t>
@@ -125,15 +125,15 @@
     <t>Validated length limit of 6 characters successfully</t>
   </si>
   <si>
+    <t>2026-07-22T04:27:29.559Z</t>
+  </si>
+  <si>
     <t>Registration Password Boundary Check - Length 7</t>
   </si>
   <si>
     <t>Validated length limit of 7 characters successfully</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:54.078Z</t>
-  </si>
-  <si>
     <t>Registration Password Boundary Check - Length 8</t>
   </si>
   <si>
@@ -260,15 +260,15 @@
     <t>Successfully tested phone input constraint with 18 digits</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:54.079Z</t>
-  </si>
-  <si>
     <t>Phone digits length validation - Length 19</t>
   </si>
   <si>
     <t>Successfully tested phone input constraint with 19 digits</t>
   </si>
   <si>
+    <t>2026-07-22T04:27:29.560Z</t>
+  </si>
+  <si>
     <t>Phone digits length validation - Length 20</t>
   </si>
   <si>
@@ -335,9 +335,6 @@
     <t>Auth Helper Check - Scenario 6</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:54.080Z</t>
-  </si>
-  <si>
     <t>Auth Helper Check - Scenario 7</t>
   </si>
   <si>
@@ -356,10 +353,11 @@
     <t>Language dropdown trigger is clickable (aria-label="Select language")</t>
   </si>
   <si>
-    <t>Language switch button found: 🇬🇧English</t>
-  </si>
-  <si>
-    <t>2026-06-18T08:52:54.201Z</t>
+    <t xml:space="preserve">Language switch button found: 🇬🇧
+English</t>
+  </si>
+  <si>
+    <t>2026-07-22T04:27:29.697Z</t>
   </si>
   <si>
     <t>Switch page UI language to: [EN]</t>
@@ -371,7 +369,7 @@
     <t>Language switcher clicked for en</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:55.326Z</t>
+    <t>2026-07-22T04:27:31.140Z</t>
   </si>
   <si>
     <t>Switch page UI language to: [HI]</t>
@@ -383,7 +381,7 @@
     <t>Language switcher clicked for hi</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:56.426Z</t>
+    <t>2026-07-22T04:27:32.532Z</t>
   </si>
   <si>
     <t>Switch page UI language to: [TE]</t>
@@ -395,7 +393,7 @@
     <t>Language switcher clicked for te</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:57.574Z</t>
+    <t>2026-07-22T04:27:33.893Z</t>
   </si>
   <si>
     <t>Switch page UI language to: [ES]</t>
@@ -407,7 +405,7 @@
     <t>Language switcher clicked for es</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:58.726Z</t>
+    <t>2026-07-22T04:27:35.293Z</t>
   </si>
   <si>
     <t>Switch page UI language to: [TA]</t>
@@ -419,7 +417,7 @@
     <t>Language switcher clicked for ta</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:59.977Z</t>
+    <t>2026-07-22T04:27:37.516Z</t>
   </si>
   <si>
     <t>Switch page UI language to: [KN]</t>
@@ -431,7 +429,7 @@
     <t>Language switcher clicked for kn</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:01.173Z</t>
+    <t>2026-07-22T04:27:39.326Z</t>
   </si>
   <si>
     <t>Switch page UI language to: [MR]</t>
@@ -443,7 +441,7 @@
     <t>Language switcher clicked for mr</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:02.385Z</t>
+    <t>2026-07-22T04:27:41.326Z</t>
   </si>
   <si>
     <t>i18n Translation Key Verification - [brand]</t>
@@ -485,6 +483,9 @@
     <t>Text key "forgotPassword" returns non-empty translation content for active language</t>
   </si>
   <si>
+    <t>2026-07-22T04:27:41.327Z</t>
+  </si>
+  <si>
     <t>i18n Translation Key Verification - [dontHaveAccount]</t>
   </si>
   <si>
@@ -509,9 +510,6 @@
     <t>Text key "phoneLabel" returns non-empty translation content for active language</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:02.386Z</t>
-  </si>
-  <si>
     <t>i18n Translation Key Verification - [emailLabel]</t>
   </si>
   <si>
@@ -560,7 +558,7 @@
     <t>Route successfully protected from unauthenticated access</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:03.188Z</t>
+    <t>2026-07-22T04:27:43.642Z</t>
   </si>
   <si>
     <t>Verify Weather Widget elements presence</t>
@@ -572,9 +570,6 @@
     <t>Component checks out: Weather components styled properly with micro-animations</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:03.189Z</t>
-  </si>
-  <si>
     <t>Verify Seasonal Risk Advisor display</t>
   </si>
   <si>
@@ -671,9 +666,6 @@
     <t>Dashboard Widget Parameterized Check - Widget ID 30</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:03.190Z</t>
-  </si>
-  <si>
     <t>Crop Scanner</t>
   </si>
   <si>
@@ -722,6 +714,9 @@
     <t>Verified state hooks mapping for Potato</t>
   </si>
   <si>
+    <t>2026-07-22T04:27:43.643Z</t>
+  </si>
+  <si>
     <t>Scan page test - Selecting Crop: Corn</t>
   </si>
   <si>
@@ -797,12 +792,12 @@
     <t>Disease Database Key Verification - Index 26</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:03.191Z</t>
-  </si>
-  <si>
     <t>Disease Database Key Verification - Index 27</t>
   </si>
   <si>
+    <t>2026-07-22T04:27:43.644Z</t>
+  </si>
+  <si>
     <t>Disease Database Key Verification - Index 28</t>
   </si>
   <si>
@@ -875,9 +870,6 @@
     <t>Crop Scanner UI Element Reactivity - Check 49</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:03.192Z</t>
-  </si>
-  <si>
     <t>Crop Scanner UI Element Reactivity - Check 50</t>
   </si>
   <si>
@@ -938,9 +930,6 @@
     <t>ChatBot Flow Edge Case Check - Scenario 10</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:03.193Z</t>
-  </si>
-  <si>
     <t>ChatBot Flow Edge Case Check - Scenario 11</t>
   </si>
   <si>
@@ -974,6 +963,9 @@
     <t>ChatBot Flow Edge Case Check - Scenario 21</t>
   </si>
   <si>
+    <t>2026-07-22T04:27:43.645Z</t>
+  </si>
+  <si>
     <t>ChatBot Flow Edge Case Check - Scenario 22</t>
   </si>
   <si>
@@ -983,9 +975,6 @@
     <t>ChatBot Flow Edge Case Check - Scenario 24</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:03.194Z</t>
-  </si>
-  <si>
     <t>ChatBot Flow Edge Case Check - Scenario 25</t>
   </si>
   <si>
@@ -1077,9 +1066,6 @@
   </si>
   <si>
     <t>Hotspot Map Layout Verification - Test 18</t>
-  </si>
-  <si>
-    <t>2026-06-18T08:53:03.195Z</t>
   </si>
   <si>
     <t>Hotspot Map Layout Verification - Test 19</t>
@@ -1602,7 +1588,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="5">
-        <v>2031</v>
+        <v>9189</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>12</v>
@@ -1628,7 +1614,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="5">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>17</v>
@@ -1654,7 +1640,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="5">
-        <v>609</v>
+        <v>925</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -1680,7 +1666,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="5">
-        <v>250</v>
+        <v>388</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>25</v>
@@ -1790,7 +1776,7 @@
         <v>36</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1801,7 +1787,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>35</v>
@@ -1813,10 +1799,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1842,7 +1828,7 @@
         <v>41</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1868,7 +1854,7 @@
         <v>43</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1894,7 +1880,7 @@
         <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1920,7 +1906,7 @@
         <v>47</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1946,7 +1932,7 @@
         <v>49</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1972,7 +1958,7 @@
         <v>51</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1998,7 +1984,7 @@
         <v>53</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2024,7 +2010,7 @@
         <v>56</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2050,7 +2036,7 @@
         <v>58</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2076,7 +2062,7 @@
         <v>60</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2102,7 +2088,7 @@
         <v>62</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2128,7 +2114,7 @@
         <v>65</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2154,7 +2140,7 @@
         <v>67</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2180,7 +2166,7 @@
         <v>69</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2206,7 +2192,7 @@
         <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2232,7 +2218,7 @@
         <v>73</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2258,7 +2244,7 @@
         <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2284,7 +2270,7 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2310,7 +2296,7 @@
         <v>79</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2336,7 +2322,7 @@
         <v>81</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2347,7 +2333,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>55</v>
@@ -2359,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2388,7 +2374,7 @@
         <v>86</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2414,7 +2400,7 @@
         <v>89</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2440,7 +2426,7 @@
         <v>89</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2466,7 +2452,7 @@
         <v>89</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2492,7 +2478,7 @@
         <v>89</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2518,7 +2504,7 @@
         <v>89</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2544,7 +2530,7 @@
         <v>89</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2570,7 +2556,7 @@
         <v>89</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2596,7 +2582,7 @@
         <v>89</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2622,7 +2608,7 @@
         <v>89</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2648,7 +2634,7 @@
         <v>89</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2674,7 +2660,7 @@
         <v>101</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2700,7 +2686,7 @@
         <v>101</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2726,7 +2712,7 @@
         <v>101</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2752,7 +2738,7 @@
         <v>101</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2778,7 +2764,7 @@
         <v>101</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2804,7 +2790,7 @@
         <v>101</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2815,7 +2801,7 @@
         <v>14</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>100</v>
@@ -2830,7 +2816,7 @@
         <v>101</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2841,7 +2827,7 @@
         <v>14</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>100</v>
@@ -2856,7 +2842,7 @@
         <v>101</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2867,7 +2853,7 @@
         <v>14</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>100</v>
@@ -2882,7 +2868,7 @@
         <v>101</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2890,25 +2876,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="5">
+        <v>137</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="5">
-        <v>121</v>
-      </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2916,25 +2902,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="5">
+        <v>1442</v>
+      </c>
+      <c r="G53" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="5">
-        <v>1125</v>
-      </c>
-      <c r="G53" s="3" t="s">
+      <c r="H53" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2942,25 +2928,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="5">
+        <v>1392</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1100</v>
-      </c>
-      <c r="G54" s="3" t="s">
+      <c r="H54" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2968,25 +2954,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="5">
+        <v>1361</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="5">
-        <v>1148</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="H55" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2994,25 +2980,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="5">
+        <v>1400</v>
+      </c>
+      <c r="G56" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="5">
-        <v>1152</v>
-      </c>
-      <c r="G56" s="3" t="s">
+      <c r="H56" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3020,25 +3006,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="5">
+        <v>2223</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="5">
-        <v>1251</v>
-      </c>
-      <c r="G57" s="3" t="s">
+      <c r="H57" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3046,25 +3032,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="5">
+        <v>1809</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="5">
-        <v>1196</v>
-      </c>
-      <c r="G58" s="3" t="s">
+      <c r="H58" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3072,25 +3058,25 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="5">
+        <v>1999</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="5">
-        <v>1211</v>
-      </c>
-      <c r="G59" s="3" t="s">
+      <c r="H59" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3098,25 +3084,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="E60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="5">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="H60" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3124,14 +3110,14 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="E61" s="4" t="s">
         <v>11</v>
       </c>
@@ -3139,10 +3125,10 @@
         <v>0</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3150,14 +3136,14 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="E62" s="4" t="s">
         <v>11</v>
       </c>
@@ -3165,10 +3151,10 @@
         <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3176,14 +3162,14 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="E63" s="4" t="s">
         <v>11</v>
       </c>
@@ -3191,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3202,14 +3188,14 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C64" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="E64" s="4" t="s">
         <v>11</v>
       </c>
@@ -3217,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3228,25 +3214,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="5">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="5">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3254,7 +3240,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>157</v>
@@ -3269,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3280,7 +3266,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>159</v>
@@ -3295,10 +3281,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3306,7 +3292,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>161</v>
@@ -3321,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3332,7 +3318,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>163</v>
@@ -3347,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3358,14 +3344,14 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="E70" s="4" t="s">
         <v>11</v>
       </c>
@@ -3373,10 +3359,10 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3384,14 +3370,14 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="E71" s="4" t="s">
         <v>11</v>
       </c>
@@ -3399,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3410,14 +3396,14 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="E72" s="4" t="s">
         <v>11</v>
       </c>
@@ -3425,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3436,14 +3422,14 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="E73" s="4" t="s">
         <v>11</v>
       </c>
@@ -3451,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3462,14 +3448,14 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E74" s="4" t="s">
         <v>11</v>
       </c>
@@ -3477,10 +3463,10 @@
         <v>0</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3488,14 +3474,14 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="E75" s="4" t="s">
         <v>11</v>
       </c>
@@ -3503,10 +3489,10 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3514,25 +3500,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="E76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="5">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="5">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="H76" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3540,14 +3526,14 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="E77" s="4" t="s">
         <v>11</v>
       </c>
@@ -3555,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3566,14 +3552,14 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="E78" s="4" t="s">
         <v>11</v>
       </c>
@@ -3581,10 +3567,10 @@
         <v>0</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3592,14 +3578,14 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="E79" s="4" t="s">
         <v>11</v>
       </c>
@@ -3607,10 +3593,10 @@
         <v>0</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3618,14 +3604,14 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="E80" s="4" t="s">
         <v>11</v>
       </c>
@@ -3633,10 +3619,10 @@
         <v>0</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3644,25 +3630,25 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C81" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="E81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="5">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" s="5">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3670,7 +3656,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>157</v>
@@ -3685,10 +3671,10 @@
         <v>0</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3696,7 +3682,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>159</v>
@@ -3711,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3722,7 +3708,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>161</v>
@@ -3737,10 +3723,10 @@
         <v>0</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3748,7 +3734,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>163</v>
@@ -3763,10 +3749,10 @@
         <v>0</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3774,14 +3760,14 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C86" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="E86" s="4" t="s">
         <v>11</v>
       </c>
@@ -3789,10 +3775,10 @@
         <v>0</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3800,14 +3786,14 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="E87" s="4" t="s">
         <v>11</v>
       </c>
@@ -3815,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3826,14 +3812,14 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C88" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="E88" s="4" t="s">
         <v>11</v>
       </c>
@@ -3841,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3852,14 +3838,14 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C89" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="E89" s="4" t="s">
         <v>11</v>
       </c>
@@ -3867,10 +3853,10 @@
         <v>0</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3878,14 +3864,14 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E90" s="4" t="s">
         <v>11</v>
       </c>
@@ -3893,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3904,14 +3890,14 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="E91" s="4" t="s">
         <v>11</v>
       </c>
@@ -3919,10 +3905,10 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3930,25 +3916,25 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="E92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="5">
+        <v>2315</v>
+      </c>
+      <c r="G92" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="5">
-        <v>802</v>
-      </c>
-      <c r="G92" s="3" t="s">
+      <c r="H92" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3956,25 +3942,25 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C93" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="E93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="5">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E93" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" s="5">
-        <v>0</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="H93" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3982,25 +3968,25 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C94" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="5">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" s="5">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="H94" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4008,25 +3994,25 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C95" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="5">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" s="5">
-        <v>0</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="H95" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4034,13 +4020,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>11</v>
@@ -4049,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4060,13 +4046,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>11</v>
@@ -4075,10 +4061,10 @@
         <v>0</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4086,13 +4072,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>11</v>
@@ -4101,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4112,13 +4098,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>11</v>
@@ -4127,10 +4113,10 @@
         <v>0</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4138,13 +4124,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>11</v>
@@ -4153,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4164,13 +4150,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>11</v>
@@ -4179,10 +4165,10 @@
         <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4190,13 +4176,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>11</v>
@@ -4205,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4216,13 +4202,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>11</v>
@@ -4231,10 +4217,10 @@
         <v>0</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4242,13 +4228,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>11</v>
@@ -4257,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4268,13 +4254,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>11</v>
@@ -4283,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4294,13 +4280,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>11</v>
@@ -4309,10 +4295,10 @@
         <v>0</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4320,13 +4306,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>11</v>
@@ -4335,10 +4321,10 @@
         <v>0</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4346,13 +4332,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>11</v>
@@ -4361,10 +4347,10 @@
         <v>0</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4372,13 +4358,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>11</v>
@@ -4387,10 +4373,10 @@
         <v>0</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4398,13 +4384,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>11</v>
@@ -4413,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4424,13 +4410,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>11</v>
@@ -4439,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4450,13 +4436,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>11</v>
@@ -4465,10 +4451,10 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4476,13 +4462,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>11</v>
@@ -4491,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4502,13 +4488,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>11</v>
@@ -4517,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4528,13 +4514,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>11</v>
@@ -4543,10 +4529,10 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4554,13 +4540,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>11</v>
@@ -4569,10 +4555,10 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4580,13 +4566,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>11</v>
@@ -4595,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4606,13 +4592,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>11</v>
@@ -4621,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4632,13 +4618,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>11</v>
@@ -4647,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4658,13 +4644,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>11</v>
@@ -4673,10 +4659,10 @@
         <v>0</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4684,13 +4670,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>11</v>
@@ -4699,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4710,25 +4696,25 @@
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="5">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" s="5">
-        <v>0</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="H122" s="2" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4736,13 +4722,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>11</v>
@@ -4751,10 +4737,10 @@
         <v>0</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4762,13 +4748,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>11</v>
@@ -4777,10 +4763,10 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4788,13 +4774,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>11</v>
@@ -4803,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4814,25 +4800,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C126" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="5">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H126" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" s="5">
-        <v>0</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4840,25 +4826,25 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C127" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="5">
+        <v>0</v>
+      </c>
+      <c r="G127" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" s="5">
-        <v>0</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="H127" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4866,25 +4852,25 @@
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C128" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="5">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" s="5">
-        <v>0</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="H128" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4892,25 +4878,25 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C129" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" s="5">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" s="5">
-        <v>0</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="H129" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4918,25 +4904,25 @@
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C130" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" s="5">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" s="5">
-        <v>0</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="H130" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4944,13 +4930,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>11</v>
@@ -4959,10 +4945,10 @@
         <v>0</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4970,25 +4956,25 @@
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C132" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="5">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="5">
-        <v>0</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4996,25 +4982,25 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C133" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="5">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" s="5">
-        <v>0</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="H133" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5022,25 +5008,25 @@
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C134" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="5">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" s="5">
-        <v>0</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="H134" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5048,25 +5034,25 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C135" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" s="5">
+        <v>0</v>
+      </c>
+      <c r="G135" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F135" s="5">
-        <v>0</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="H135" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5074,25 +5060,25 @@
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C136" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="5">
+        <v>0</v>
+      </c>
+      <c r="G136" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D136" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" s="5">
-        <v>0</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="H136" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5100,25 +5086,25 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C137" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="5">
+        <v>0</v>
+      </c>
+      <c r="G137" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" s="5">
-        <v>0</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="H137" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5126,13 +5112,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>11</v>
@@ -5141,10 +5127,10 @@
         <v>0</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5152,13 +5138,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>11</v>
@@ -5167,10 +5153,10 @@
         <v>0</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5178,13 +5164,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>11</v>
@@ -5193,10 +5179,10 @@
         <v>0</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5204,13 +5190,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>11</v>
@@ -5219,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5230,13 +5216,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>11</v>
@@ -5245,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5256,13 +5242,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>11</v>
@@ -5271,10 +5257,10 @@
         <v>0</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5282,13 +5268,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>11</v>
@@ -5297,10 +5283,10 @@
         <v>0</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5308,13 +5294,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>11</v>
@@ -5323,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5334,13 +5320,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>11</v>
@@ -5349,10 +5335,10 @@
         <v>0</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5360,13 +5346,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>11</v>
@@ -5375,10 +5361,10 @@
         <v>0</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5386,13 +5372,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>11</v>
@@ -5401,10 +5387,10 @@
         <v>0</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5412,13 +5398,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>11</v>
@@ -5427,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5438,13 +5424,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>11</v>
@@ -5453,10 +5439,10 @@
         <v>0</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5464,13 +5450,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>11</v>
@@ -5479,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5490,13 +5476,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>11</v>
@@ -5505,10 +5491,10 @@
         <v>0</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5516,13 +5502,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>11</v>
@@ -5531,10 +5517,10 @@
         <v>0</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5542,13 +5528,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>11</v>
@@ -5557,10 +5543,10 @@
         <v>0</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5568,13 +5554,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>11</v>
@@ -5583,10 +5569,10 @@
         <v>0</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5594,13 +5580,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>11</v>
@@ -5609,10 +5595,10 @@
         <v>0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5620,25 +5606,25 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C157" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="5">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D157" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E157" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F157" s="5">
-        <v>0</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="H157" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5646,13 +5632,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>11</v>
@@ -5661,10 +5647,10 @@
         <v>0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5672,13 +5658,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>11</v>
@@ -5687,10 +5673,10 @@
         <v>0</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5698,13 +5684,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>11</v>
@@ -5713,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5724,13 +5710,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>11</v>
@@ -5739,10 +5725,10 @@
         <v>0</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5750,13 +5736,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>11</v>
@@ -5765,10 +5751,10 @@
         <v>0</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5776,13 +5762,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>11</v>
@@ -5791,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5802,13 +5788,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>11</v>
@@ -5817,10 +5803,10 @@
         <v>0</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5828,13 +5814,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>11</v>
@@ -5843,10 +5829,10 @@
         <v>0</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5854,13 +5840,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>11</v>
@@ -5869,10 +5855,10 @@
         <v>0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5880,13 +5866,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>11</v>
@@ -5895,10 +5881,10 @@
         <v>0</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5906,13 +5892,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>11</v>
@@ -5921,10 +5907,10 @@
         <v>0</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5932,13 +5918,13 @@
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>11</v>
@@ -5947,10 +5933,10 @@
         <v>0</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5958,13 +5944,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>11</v>
@@ -5973,10 +5959,10 @@
         <v>0</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5984,13 +5970,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>11</v>
@@ -5999,10 +5985,10 @@
         <v>0</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6010,25 +5996,25 @@
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="5">
+        <v>0</v>
+      </c>
+      <c r="G172" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F172" s="5">
-        <v>0</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="H172" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6036,13 +6022,13 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>11</v>
@@ -6051,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6062,13 +6048,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>11</v>
@@ -6077,10 +6063,10 @@
         <v>0</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6088,13 +6074,13 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>11</v>
@@ -6103,10 +6089,10 @@
         <v>0</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6114,13 +6100,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>11</v>
@@ -6129,10 +6115,10 @@
         <v>0</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6140,13 +6126,13 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>11</v>
@@ -6155,10 +6141,10 @@
         <v>0</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6166,13 +6152,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>11</v>
@@ -6181,10 +6167,10 @@
         <v>0</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6192,13 +6178,13 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>11</v>
@@ -6207,10 +6193,10 @@
         <v>0</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6218,13 +6204,13 @@
         <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>11</v>
@@ -6233,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6244,25 +6230,25 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F181" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6270,13 +6256,13 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>11</v>
@@ -6285,10 +6271,10 @@
         <v>0</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6296,13 +6282,13 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>11</v>
@@ -6311,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6322,13 +6308,13 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>11</v>
@@ -6337,10 +6323,10 @@
         <v>0</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6348,13 +6334,13 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>11</v>
@@ -6363,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6374,13 +6360,13 @@
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>11</v>
@@ -6389,10 +6375,10 @@
         <v>0</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6400,13 +6386,13 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>11</v>
@@ -6415,10 +6401,10 @@
         <v>0</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6426,13 +6412,13 @@
         <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>11</v>
@@ -6441,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6452,13 +6438,13 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>11</v>
@@ -6467,10 +6453,10 @@
         <v>0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6478,13 +6464,13 @@
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>11</v>
@@ -6493,10 +6479,10 @@
         <v>0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6504,13 +6490,13 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>11</v>
@@ -6519,10 +6505,10 @@
         <v>0</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6530,13 +6516,13 @@
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>11</v>
@@ -6545,10 +6531,10 @@
         <v>0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6556,13 +6542,13 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>11</v>
@@ -6571,10 +6557,10 @@
         <v>0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6582,13 +6568,13 @@
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>11</v>
@@ -6597,10 +6583,10 @@
         <v>0</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6608,13 +6594,13 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>11</v>
@@ -6623,10 +6609,10 @@
         <v>0</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6634,13 +6620,13 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>11</v>
@@ -6649,10 +6635,10 @@
         <v>0</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6660,13 +6646,13 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>11</v>
@@ -6675,10 +6661,10 @@
         <v>0</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6686,13 +6672,13 @@
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>11</v>
@@ -6701,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6712,13 +6698,13 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>11</v>
@@ -6727,10 +6713,10 @@
         <v>0</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6738,13 +6724,13 @@
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>11</v>
@@ -6753,10 +6739,10 @@
         <v>0</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6764,13 +6750,13 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>11</v>
@@ -6779,10 +6765,10 @@
         <v>0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6790,13 +6776,13 @@
         <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>11</v>
@@ -6805,10 +6791,10 @@
         <v>0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6816,13 +6802,13 @@
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C203" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C203" s="3" t="s">
-        <v>334</v>
-      </c>
       <c r="D203" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>11</v>
@@ -6831,10 +6817,10 @@
         <v>0</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6842,13 +6828,13 @@
         <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>11</v>
@@ -6857,10 +6843,10 @@
         <v>0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6868,13 +6854,13 @@
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>11</v>
@@ -6883,10 +6869,10 @@
         <v>0</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6894,13 +6880,13 @@
         <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>11</v>
@@ -6909,10 +6895,10 @@
         <v>0</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6920,13 +6906,13 @@
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>11</v>
@@ -6935,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6946,13 +6932,13 @@
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>11</v>
@@ -6961,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6972,13 +6958,13 @@
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>11</v>
@@ -6987,10 +6973,10 @@
         <v>0</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6998,13 +6984,13 @@
         <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>11</v>
@@ -7013,10 +6999,10 @@
         <v>0</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7024,13 +7010,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>11</v>
@@ -7039,10 +7025,10 @@
         <v>0</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7050,13 +7036,13 @@
         <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E212" s="4" t="s">
         <v>11</v>
@@ -7065,10 +7051,10 @@
         <v>0</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7076,13 +7062,13 @@
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>11</v>
@@ -7091,10 +7077,10 @@
         <v>0</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7102,13 +7088,13 @@
         <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>11</v>
@@ -7117,10 +7103,10 @@
         <v>0</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7128,13 +7114,13 @@
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>11</v>
@@ -7143,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7154,13 +7140,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>11</v>
@@ -7169,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7180,13 +7166,13 @@
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>11</v>
@@ -7195,10 +7181,10 @@
         <v>0</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7206,13 +7192,13 @@
         <v>217</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>11</v>
@@ -7221,10 +7207,10 @@
         <v>0</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7232,13 +7218,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>11</v>
@@ -7247,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7258,13 +7244,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>11</v>
@@ -7273,10 +7259,10 @@
         <v>0</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7284,13 +7270,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E221" s="4" t="s">
         <v>11</v>
@@ -7299,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -7322,15 +7308,15 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B2" s="8">
         <v>220</v>
@@ -7338,7 +7324,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B3" s="8">
         <v>220</v>
@@ -7346,7 +7332,7 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B4" s="8">
         <v>0</v>
@@ -7354,10 +7340,10 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
